--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260715.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>154,617,148</t>
+          <t>432,781,233</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>432,781,233</t>
+          <t>154,617,148</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>25,579,761</t>
+          <t>31,774,801</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>31,774,801</t>
+          <t>25,579,761</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>33,965,745</t>
+          <t>11,194,543</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>11,194,543</t>
+          <t>33,965,745</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
